--- a/materials/generated_outputs/Weekly Schedules.xlsx
+++ b/materials/generated_outputs/Weekly Schedules.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -432,7 +432,8 @@
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
-    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,6 +464,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Additional Events</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Instructor Flags</t>
         </is>
       </c>
@@ -487,7 +493,8 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Lab 1: Prerequisite may be same-day: M1.L01: Classify and Analyze Variables (first covered Lecture 2) | Lab 1: Prerequisite may be same-day: M1.L02: Evaluate Study Design and Its Implications (first covered Lecture 2) | Lab 1: Prerequisite may be same-day: M1.L03: Use R for Data Management and Exploration (first covered Lecture 2)</t>
         </is>
@@ -517,7 +524,8 @@
           <t>Lab 2: Lab1 in-lab activity submission | Tutorial 1 | Tutorial 2 (pre-lab for lab2)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Lecture 3: Near Labor Day Holiday, Classes Suspended</t>
         </is>
@@ -548,6 +556,7 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -574,6 +583,7 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -600,6 +610,7 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -626,6 +637,7 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -651,7 +663,8 @@
           <t>Project1-2: Lab5 in-lab activity submission</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Lecture 16: Near Indigenous People's Day Holiday, Classes Suspended | Lecture 16: Substitute a Monday schedule of classes | Quiz 2: Near Indigenous People's Day Holiday, Classes Suspended | Quiz 2: Near Substitute a Monday schedule of classes</t>
         </is>
@@ -681,7 +694,8 @@
           <t>Project2-1: Project1 Video</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Project2-1: Prerequisite not yet covered: M3.L05: Distinguish Statistical vs. Practical Significance (first covered Lecture 28) | Project2-1: Prerequisite not yet covered: M4.L01: Inference for a Difference in Proportions (first covered Lecture 21) | Project2-1: Prerequisite not yet covered: M4.L02: Conduct and Interpret Chi-Square Tests (first covered Lecture 22) | Project2-1: Prerequisite not yet covered: M4.L04: Conduct and Interpret t-Tests (first covered Lecture 24) | Project2-1: Prerequisite not yet covered: M4.L05: Explain Hypothesis Testing and Its Limitations (first covered Lecture 28)</t>
         </is>
@@ -711,7 +725,8 @@
           <t>Lab 6: Lab6 in-lab activity submission | Tutorial 6 (pre-lab for lab6) | Project2 Outline</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Lab 6: Prerequisite not yet covered: M3.L05: Distinguish Statistical vs. Practical Significance (first covered Lecture 28)</t>
         </is>
@@ -741,7 +756,8 @@
           <t>Project2-2: Lab6 in-lab activity submission</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Quiz 3: Prerequisite not yet covered: M3.L05: Distinguish Statistical vs. Practical Significance (first covered Lecture 28) | Project2-2: Prerequisite not yet covered: M3.L05: Distinguish Statistical vs. Practical Significance (first covered Lecture 28) | Project2-2: Prerequisite not yet covered: M4.L05: Explain Hypothesis Testing and Its Limitations (first covered Lecture 28)</t>
         </is>
@@ -771,7 +787,8 @@
           <t>Project2-3: Project2 Progress Report</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Project2-3: Prerequisite may be same-day: M3.L05: Distinguish Statistical vs. Practical Significance (first covered Lecture 28) | Project2-3: Prerequisite may be same-day: M4.L05: Explain Hypothesis Testing and Its Limitations (first covered Lecture 28)</t>
         </is>
@@ -801,7 +818,8 @@
           <t>Lab 7: Project2 writeup | Tutorial 7 (pre-lab for lab7)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>Lab 7: Prerequisite may be same-day: M5.L03: Comparing Bayesian and Frequentist Approaches (first covered Lecture 31)</t>
         </is>
@@ -831,7 +849,8 @@
           <t>Lab 8: Project2 Resubmission</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>Lecture 32: Near Thanksgiving Recess | Lab 8: Near Thanksgiving Recess | Lab 8: Classes Resume | Lab 8: Missing prerequisite metadata: add learning-objective tags for Lab 8</t>
         </is>
@@ -853,7 +872,8 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>Quiz 4: Near Thanksgiving Recess | Quiz 4: Classes Resume | Lecture 33: Near Classes Resume</t>
         </is>
@@ -875,7 +895,8 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>Quiz 5: Near Last Day of Classes; Second Seven-Week Session Ends | Quiz 5: Near Study Period | Lecture 36: Last Day of Classes; Second Seven-Week Session Ends | Lecture 36: Near Study Period</t>
         </is>

--- a/materials/generated_outputs/Weekly Schedules.xlsx
+++ b/materials/generated_outputs/Weekly Schedules.xlsx
@@ -432,7 +432,7 @@
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -636,7 +636,11 @@
           <t>Lab 5: Lab4 in-lab activity submission | Tutorial 5 (pre-lab for lab5)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Midterm Review, 5:00PM-6:00PM</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">

--- a/materials/generated_outputs/Weekly Schedules.xlsx
+++ b/materials/generated_outputs/Weekly Schedules.xlsx
@@ -430,7 +430,7 @@
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
@@ -489,7 +489,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lab 1 (Lecture 1)</t>
+          <t>Lab 1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -516,7 +516,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lab 2 (Lecture 3)</t>
+          <t>Lab 2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lab 3 (Lecture 6)</t>
+          <t>Lab 3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lab 4 (Lecture 11)</t>
+          <t>Lab 4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lab 5 (Lecture 14)</t>
+          <t>Lab 5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lab 6 (Lecture 22)</t>
+          <t>Lab 6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lab 7 (Lecture 30)</t>
+          <t>Lab 7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">

--- a/materials/generated_outputs/Weekly Schedules.xlsx
+++ b/materials/generated_outputs/Weekly Schedules.xlsx
@@ -492,7 +492,11 @@
           <t>Lab 1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Lab 1: Tutorial 0 hash code submitted to Blackboard</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>

--- a/materials/generated_outputs/Weekly Schedules.xlsx
+++ b/materials/generated_outputs/Weekly Schedules.xlsx
@@ -431,7 +431,7 @@
     <col width="37" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="74" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
@@ -492,11 +492,7 @@
           <t>Lab 1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Lab 1: Tutorial 0 hash code submitted to Blackboard</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
@@ -525,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lab 2: Lab1 in-lab activity submission | Tutorial 1 | Tutorial 2 (pre-lab for lab2)</t>
+          <t>Lab 2: Lab2 in-lab activity submission | Tutorial 2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -556,7 +552,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lab 3: Lab2 in-lab activity submission | Tutorial 3 (pre-lab for lab3)</t>
+          <t>Lab 3: Lab3 in-lab activity submission | Tutorial 3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -568,12 +564,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lecture 8, Quiz 1, Lecture 9</t>
+          <t>Quiz 1, Lecture 8, Lecture 9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lecture 8: Sampling from a small population, Random Variables (Chapters 3.3–3.4); Quiz 1: confirmed; Lecture 9: Continuous Distributions (Chapter 3.5)</t>
+          <t>Quiz 1: confirmed; Lecture 8: Sampling from a small population, Random Variables (Chapters 3.3–3.4); Lecture 9: Continuous Distributions (Chapter 3.5)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -583,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Project1-1: Lab3 in-lab activity submission</t>
+          <t>Project1-1: Project 1 plan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -610,7 +606,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lab 4: Project 1 Outline | Tutorial 4 (pre-lab for lab4)</t>
+          <t>Lab 4: Project 1 Outline | Lab4 in-lab activity submission | Tutorial 4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -637,7 +633,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lab 5: Lab4 in-lab activity submission | Tutorial 5 (pre-lab for lab5)</t>
+          <t>Lab 5: Lab5 in-lab activity submission | Tutorial 5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -653,12 +649,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lecture 16, Quiz 2, Lecture 17</t>
+          <t>Quiz 2, Lecture 16, Lecture 17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lecture 16: Point estimates and sampling variability, continued (Chapter 5.1); Quiz 2: in the lecture time; Lecture 17: Confidence intervals (Chapter 5.2)</t>
+          <t>Quiz 2: in the lecture time; Lecture 16: Point estimates and sampling variability, continued (Chapter 5.1); Lecture 17: Confidence intervals (Chapter 5.2)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -666,15 +662,11 @@
           <t>Project1-2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Project1-2: Lab5 in-lab activity submission</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lecture 16: Near Indigenous People's Day Holiday, Classes Suspended | Lecture 16: Substitute a Monday schedule of classes | Quiz 2: Near Indigenous People's Day Holiday, Classes Suspended | Quiz 2: Near Substitute a Monday schedule of classes</t>
+          <t>Quiz 2: Near Indigenous People's Day Holiday, Classes Suspended | Quiz 2: Substitute a Monday schedule of classes | Lecture 16: Near Indigenous People's Day Holiday, Classes Suspended | Lecture 16: Near Substitute a Monday schedule of classes</t>
         </is>
       </c>
     </row>
@@ -730,7 +722,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lab 6: Lab6 in-lab activity submission | Tutorial 6 (pre-lab for lab6) | Project2 Outline</t>
+          <t>Lab 6: Lab6 in-lab activity submission | Tutorial 6 | Project2 Outline</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -746,12 +738,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lecture 24, Quiz 3, Lecture 25</t>
+          <t>Quiz 3, Lecture 24, Lecture 25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lecture 24: One-sample means with the t-distribution (Chapter 7.1); Quiz 3: tentative; Lecture 25: CIs for one-sample means, Paired data (Chapter 7.2)</t>
+          <t>Quiz 3: tentative; Lecture 24: One-sample means with the t-distribution (Chapter 7.1); Lecture 25: CIs for one-sample means, Paired data (Chapter 7.2)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -759,11 +751,7 @@
           <t>Project2-2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Project2-2: Lab6 in-lab activity submission</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
@@ -823,7 +811,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lab 7: Project2 writeup | Tutorial 7 (pre-lab for lab7)</t>
+          <t>Lab 7: Project2 writeup | Lab7 in-lab activity submission | Tutorial 7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -839,12 +827,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lecture 32</t>
+          <t>Quiz 4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lecture 32: Frequentist modeling using the likelihood function</t>
+          <t>Quiz 4: tentative</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -860,7 +848,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lecture 32: Near Thanksgiving Recess | Lab 8: Near Thanksgiving Recess | Lab 8: Classes Resume | Lab 8: Missing prerequisite metadata: add learning-objective tags for Lab 8</t>
+          <t>Quiz 4: Near Thanksgiving Recess | Lab 8: Near Thanksgiving Recess | Lab 8: Classes Resume | Lab 8: Missing prerequisite metadata: add learning-objective tags for Lab 8</t>
         </is>
       </c>
     </row>
@@ -870,12 +858,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Quiz 4, Lecture 33, Lecture 34</t>
+          <t>Lecture 32, Lecture 33, Lecture 34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Quiz 4: tentative; Lecture 33: Bayesian modeling with discrete distributions; Lecture 34: Bayesian modeling with the beta-binomial model</t>
+          <t>Lecture 32: Frequentist modeling using the likelihood function; Lecture 33: Bayesian modeling with discrete distributions; Lecture 34: Bayesian modeling with the beta-binomial model</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -883,7 +871,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Quiz 4: Near Thanksgiving Recess | Quiz 4: Classes Resume | Lecture 33: Near Classes Resume</t>
+          <t>Lecture 32: Near Thanksgiving Recess | Lecture 32: Classes Resume | Lecture 33: Near Classes Resume</t>
         </is>
       </c>
     </row>

--- a/materials/generated_outputs/Weekly Schedules.xlsx
+++ b/materials/generated_outputs/Weekly Schedules.xlsx
@@ -492,7 +492,11 @@
           <t>Lab 1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Lab 1: Lab1 in-lab activity submission | Tutorial 1</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
